--- a/mode_docx_gen/pmi_mtzt/bnt_modes/БНТ_20.xlsx
+++ b/mode_docx_gen/pmi_mtzt/bnt_modes/БНТ_20.xlsx
@@ -1496,7 +1496,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>gen_pusk_ptoc_lvttoc</t>
+          <t>gen_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
